--- a/artfynd/A 52044-2025 artfynd.xlsx
+++ b/artfynd/A 52044-2025 artfynd.xlsx
@@ -1974,7 +1974,7 @@
         <v>89736261</v>
       </c>
       <c r="B12" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 52044-2025 artfynd.xlsx
+++ b/artfynd/A 52044-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66813530</v>
+        <v>104424183</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>1174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,23 +703,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djurrödsbäcken, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434612.3391108088</v>
+        <v>434617</v>
       </c>
       <c r="R2" t="n">
-        <v>6172202.528912785</v>
+        <v>6172027</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,33 +770,38 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Stenbunden betesmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Lysell</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Lysell, Kaj Svahn</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Insektsinventering 2022 Djurrödsbäcken och Rölabackarna</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66813552</v>
+        <v>74234135</v>
       </c>
       <c r="B3" t="n">
-        <v>40958</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,42 +809,56 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>215767</v>
+        <v>100015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grå klaffmätare</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Philereme vetulata</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djurrödsbäcken, Sk</t>
+          <t>Djurröd, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434612.3391108088</v>
+        <v>434580</v>
       </c>
       <c r="R3" t="n">
-        <v>6172202.528912785</v>
+        <v>6172016</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +882,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-22</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-22</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,70 +912,81 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Lysell</t>
+          <t>Rune Gerell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Lysell, Kaj Svahn</t>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66831035</v>
+        <v>89736256</v>
       </c>
       <c r="B4" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>100015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djurrödsbäcken, Sk</t>
+          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434612.3391108088</v>
+        <v>434588</v>
       </c>
       <c r="R4" t="n">
-        <v>6172202.528912785</v>
+        <v>6172040</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +1010,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-07-22</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-07-22</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,54 +1040,53 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Lysell</t>
+          <t>Rune Gerell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Lysell, Kaj Svahn</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89736314</v>
+        <v>74234351</v>
       </c>
       <c r="B5" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>100085</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Bechsteins fladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis bechsteinii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>129</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1079,17 +1106,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+          <t>Djurröd, Skåne, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434587.873325358</v>
+        <v>434580</v>
       </c>
       <c r="R5" t="n">
-        <v>6172040.011027419</v>
+        <v>6172016</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,17 +1140,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1151,50 +1178,41 @@
           <t>Rune Gerell, Karin Gerell Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89736282</v>
+        <v>74234331</v>
       </c>
       <c r="B6" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100111</v>
+        <v>100087</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1214,17 +1232,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+          <t>Djurröd, Skåne, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434587.873325358</v>
+        <v>434580</v>
       </c>
       <c r="R6" t="n">
-        <v>6172040.011027419</v>
+        <v>6172016</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1248,17 +1266,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1286,50 +1304,41 @@
           <t>Rune Gerell, Karin Gerell Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89736263</v>
+        <v>74234308</v>
       </c>
       <c r="B7" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,17 +1358,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+          <t>Djurröd, Skåne, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434587.873325358</v>
+        <v>434580</v>
       </c>
       <c r="R7" t="n">
-        <v>6172040.011027419</v>
+        <v>6172016</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,17 +1392,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1421,23 +1430,14 @@
           <t>Rune Gerell, Karin Gerell Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
-        </is>
-      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89736279</v>
+        <v>89736314</v>
       </c>
       <c r="B8" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,26 +1445,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434587.873325358</v>
+        <v>434588</v>
       </c>
       <c r="R8" t="n">
-        <v>6172040.011027419</v>
+        <v>6172040</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1564,15 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89736295</v>
+        <v>89736282</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,26 +1575,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1623,10 +1618,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434587.873325358</v>
+        <v>434588</v>
       </c>
       <c r="R9" t="n">
-        <v>6172040.011027419</v>
+        <v>6172040</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1653,7 +1648,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1663,7 +1658,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1699,42 +1694,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89736250</v>
+        <v>74234347</v>
       </c>
       <c r="B10" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206002</v>
+        <v>102102</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Mustaschfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis mystacinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1754,17 +1744,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+          <t>Djurröd, Skåne, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434587.873325358</v>
+        <v>434580</v>
       </c>
       <c r="R10" t="n">
-        <v>6172040.011027419</v>
+        <v>6172016</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1788,17 +1778,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1826,82 +1816,55 @@
           <t>Rune Gerell, Karin Gerell Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89736256</v>
+        <v>66813496</v>
       </c>
       <c r="B11" t="n">
-        <v>57482</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100015</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+          <t>Djurrödsbäcken, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434587.873325358</v>
+        <v>434612</v>
       </c>
       <c r="R11" t="n">
-        <v>6172040.011027419</v>
+        <v>6172203</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1925,22 +1888,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2017-07-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2017-07-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,83 +1908,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rune Gerell</t>
+          <t>Fredrik Lysell</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rune Gerell, Karin Gerell Lundberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
-        </is>
-      </c>
+          <t>Fredrik Lysell</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89736261</v>
+        <v>66813542</v>
       </c>
       <c r="B12" t="n">
-        <v>56620</v>
+        <v>43309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206000</v>
+        <v>201146</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+          <t>Djurrödsbäcken, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434588</v>
+        <v>434612</v>
       </c>
       <c r="R12" t="n">
-        <v>6172040</v>
+        <v>6172203</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2055,22 +1990,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2017-07-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2017-07-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2085,17 +2010,1590 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Fredrik Lysell</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fredrik Lysell, Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>74234337</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56824</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205991</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Större musöra</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Myotis myotis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1797)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Djurröd, Skåne, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>434580</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6172016</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Rune Gerell</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Rune Gerell, Karin Gerell Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>74234355</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Djurröd, Skåne, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>434580</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6172016</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>89736290</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>434588</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6172040</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>74234145</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djurröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>434580</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6172016</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>89736276</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>434588</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6172040</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>74234304</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Djurröd, Skåne, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>434580</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6172016</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-09-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-09-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>89736263</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>434588</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6172040</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89736261</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>434588</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6172040</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>89736250</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Djurrödsbäcken, Tomelilla kommun, Sk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>434588</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6172040</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rune Gerell</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rune Gerell, Karin Gerell Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>66831035</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Djurrödsbäcken, Sk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>434612</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6172203</v>
+      </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2017-07-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2017-07-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Fredrik Lysell</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Fredrik Lysell, Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>66813552</v>
+      </c>
+      <c r="B23" t="n">
+        <v>41656</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>215767</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grå klaffmätare</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Philereme vetulata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Djurrödsbäcken, Sk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>434612</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6172203</v>
+      </c>
+      <c r="S23" t="n">
+        <v>100</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2017-07-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2017-07-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Fredrik Lysell</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Fredrik Lysell, Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>66813530</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Djurrödsbäcken, Sk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>434612</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6172203</v>
+      </c>
+      <c r="S24" t="n">
+        <v>100</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-07-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-07-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Fredrik Lysell</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Fredrik Lysell, Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104424195</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Djurrödsbäcken, Sk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>434596</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6172027</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Andrarum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-06-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-06-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Insektsinventering 2022 Djurrödsbäcken och Rölabackarna</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 52044-2025 artfynd.xlsx
+++ b/artfynd/A 52044-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
           <t>Insektsinventering 2022 Djurrödsbäcken och Rölabackarna</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424183</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234135</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,6 +1068,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89736256</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1179,6 +1199,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234351</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1305,6 +1330,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234331</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1431,6 +1461,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234308</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1561,6 +1596,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89736314</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1691,6 +1731,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89736282</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1817,6 +1862,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234347</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1917,6 +1967,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66813496</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2019,6 +2074,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66813542</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2145,6 +2205,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234337</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2271,6 +2336,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234355</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2401,6 +2471,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89736290</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2527,6 +2602,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234145</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2657,6 +2737,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89736276</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2783,6 +2868,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74234304</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2913,6 +3003,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89736263</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3043,6 +3138,11 @@
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89736261</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3171,6 +3271,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Fladdermöss - gemensamt delprogram (uppföljning skyddade områden)</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89736250</t>
         </is>
       </c>
     </row>
@@ -3275,6 +3380,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66831035</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3377,6 +3487,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66813552</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3477,6 +3592,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66813530</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3596,8 +3716,39 @@
           <t>Insektsinventering 2022 Djurrödsbäcken och Rölabackarna</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424195</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>